--- a/results/Int Task Remove ACC 0.2/Decis_5_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Decis_5_permute.xlsx
@@ -446,7 +446,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -456,871 +456,871 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.774631704059131</v>
+        <v>0.712591945018014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.774631704059131</v>
+        <v>0.6804423127980862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7838808879546696</v>
+        <v>0.6804423127980862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7838808879546696</v>
+        <v>0.6832145917964478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7819845541999287</v>
+        <v>0.6832145917964478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7819845541999287</v>
+        <v>0.6832145917964478</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7832487767030893</v>
+        <v>0.683530647422238</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7832487767030893</v>
+        <v>0.7147052875865456</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7832487767030893</v>
+        <v>0.6618875433501759</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7829327210772992</v>
+        <v>0.6618875433501759</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6929404384747341</v>
+        <v>0.6865398821618067</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6929404384747341</v>
+        <v>0.6708994275919656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6932564941005243</v>
+        <v>0.6708994275919656</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6736610453015356</v>
+        <v>0.6708994275919656</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6736610453015356</v>
+        <v>0.5634965725676098</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6736610453015356</v>
+        <v>0.5634965725676098</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6736610453015356</v>
+        <v>0.5634965725676098</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6607027646441399</v>
+        <v>0.560543739484874</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6607027646441399</v>
+        <v>0.5578233912803039</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6607027646441399</v>
+        <v>0.5500777930169246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7463290775302678</v>
+        <v>0.5471452507741471</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7463290775302678</v>
+        <v>0.5458810282709866</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7020922951209816</v>
+        <v>0.5458810282709866</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7020922951209816</v>
+        <v>0.543720569684247</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7020922951209816</v>
+        <v>0.543720569684247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.697051225085256</v>
+        <v>0.543720569684247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.697051225085256</v>
+        <v>0.5393631977813513</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7042641028215961</v>
+        <v>0.5393631977813513</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6723084372751671</v>
+        <v>0.5393631977813513</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.653934221911631</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.653934221911631</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5976402097041114</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5894791650904009</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5824062597585183</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5824062597585183</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5954639311404553</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6521551623335979</v>
+        <v>0.5499715240415501</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6521551623335979</v>
+        <v>0.6058459629482384</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.619587676375547</v>
+        <v>0.6105867973350905</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5807647651971513</v>
+        <v>0.6105867973350905</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5807647651971513</v>
+        <v>0.6094986580532624</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5807647651971513</v>
+        <v>0.6306585650042852</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5841464572193433</v>
+        <v>0.6360992614134255</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5895194028577757</v>
+        <v>0.623639653941444</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5892033472319855</v>
+        <v>0.623323598315654</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5725964984200658</v>
+        <v>0.623323598315654</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5725964984200658</v>
+        <v>0.623323598315654</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5725964984200658</v>
+        <v>0.624411737597482</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5720524287791517</v>
+        <v>0.6067373842562341</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5720524287791517</v>
+        <v>0.6067373842562341</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.562473776668698</v>
+        <v>0.6067373842562341</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5773173858795013</v>
+        <v>0.6067373842562341</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5773173858795013</v>
+        <v>0.6067373842562341</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5773173858795013</v>
+        <v>0.6094577324608043</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5748611625069298</v>
+        <v>0.6094577324608043</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5748611625069298</v>
+        <v>0.6094577324608043</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5748611625069298</v>
+        <v>0.6094577324608043</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5748611625069298</v>
+        <v>0.594544309004043</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5748611625069298</v>
+        <v>0.5906364307931036</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5748611625069298</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5748611625069298</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4625885058925975</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4625885058925975</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4625885058925975</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5163114279386295</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5163114279386295</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5163114279386295</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5147311498096788</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5086084748304167</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5086084748304167</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5086084748304167</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5086084748304167</v>
+        <v>0.5043845409936871</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5092495278080803</v>
+        <v>0.5034363741163167</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5092495278080803</v>
+        <v>0.5034363741163167</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5092495278080803</v>
+        <v>0.5034363741163167</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5092495278080803</v>
+        <v>0.5034363741163167</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5092495278080803</v>
+        <v>0.5034363741163167</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5092495278080803</v>
+        <v>0.5034363741163167</v>
       </c>
     </row>
   </sheetData>
